--- a/Assets/Excel/物品配置表.xlsx
+++ b/Assets/Excel/物品配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>f_id</t>
   </si>
@@ -88,6 +88,15 @@
   </si>
   <si>
     <t>Item_OriginalEngraving</t>
+  </si>
+  <si>
+    <t>创世余烬</t>
+  </si>
+  <si>
+    <t>一部以文明灰烬为纸、星光为墨书写的禁忌之书，记载着宇宙诞生前被抹除的七种原初叙事。书页翻动时会发出星体坍缩的挽歌，字迹在观测的瞬间才从量子态凝为预言——它不是被阅读，而是短暂地借阅你的存在来显形。此书沉睡于时间图书馆的负一层，只有那些在命运十字路口同时走向所有方向的人，才能在意识的绝对寂静中触碰到它的烫金封面。</t>
+  </si>
+  <si>
+    <t>Item_EmbersOfGenesis</t>
   </si>
 </sst>
 </file>
@@ -1042,8 +1051,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
     <col min="2" max="2" width="42.125" customWidth="1"/>
@@ -1142,6 +1151,23 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7" s="2" customFormat="1" ht="94" customHeight="1" spans="1:5">
+      <c r="A7" s="2">
+        <v>10003</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
